--- a/results/delta/v1_to_v1_1_delta.xlsx
+++ b/results/delta/v1_to_v1_1_delta.xlsx
@@ -502,13 +502,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.795621952009657</v>
+        <v>0.7964522450687794</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1825062199655614</v>
+        <v>0.1853712976944825</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -525,13 +525,13 @@
         <v>9</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008302930591224111</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002865077728921167</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -586,40 +586,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>extratrees</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7803300993572464</v>
+        <v>0.7675390063081083</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1395906583983687</v>
+        <v>0.1342371441199022</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>extratrees</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.778291616922111</v>
+        <v>0.7675390063081083</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1366611393084907</v>
+        <v>0.1342371441199022</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.00203848243513538</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.002929519089877958</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -634,13 +634,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8124041670509727</v>
+        <v>0.8102974592286788</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2179801169523388</v>
+        <v>0.2163882894451978</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -648,13 +648,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.8124041670509727</v>
+        <v>0.8102974592286788</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2179801169523388</v>
+        <v>0.2163882894451978</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -678,13 +678,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8635755888181507</v>
+        <v>0.8665735005647537</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4197146136049616</v>
+        <v>0.4183159022170709</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8635755888181507</v>
+        <v>0.8665735005647537</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4197146136049616</v>
+        <v>0.4183159022170709</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>

--- a/results/delta/v1_to_v1_1_delta.xlsx
+++ b/results/delta/v1_to_v1_1_delta.xlsx
@@ -502,13 +502,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7964522450687794</v>
+        <v>0.795621952009657</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1853712976944825</v>
+        <v>0.1825062199655614</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -525,13 +525,13 @@
         <v>9</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.0008302930591224111</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.002865077728921167</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3">
@@ -586,17 +586,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>extratrees</t>
+          <t>random_forest</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7675390063081083</v>
+        <v>0.778291616922111</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1342371441199022</v>
+        <v>0.1366611393084907</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -613,13 +613,13 @@
         <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0.01075261061400268</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-0.002423995188588518</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
@@ -634,13 +634,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8102974592286788</v>
+        <v>0.8124041670509727</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2163882894451978</v>
+        <v>0.2179801169523388</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -657,13 +657,13 @@
         <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0.002106707822293941</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-0.001591827507141097</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
@@ -678,13 +678,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8665735005647537</v>
+        <v>0.8635755888181507</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4183159022170709</v>
+        <v>0.4197146136049616</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -701,13 +701,13 @@
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.002997911746603021</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-0.001398711387890661</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
